--- a/excel/20260805_タイムレコード_03_検証用データセット.xlsx
+++ b/excel/20260805_タイムレコード_03_検証用データセット.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Shift_JISで保存したファイル（Excelで「CSV（コンマ区切り）」を選ぶ）</t>
+          <t>Shift_JISで保存したファイル（Windows: メモ帳で開き「名前を付けて保存」→文字コード「ANSI」／Mac: ターミナルで iconv -f UTF-8 -t SHIFT_JIS 元.csv &gt; 変換後.csv）</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">

--- a/excel/20260805_タイムレコード_03_検証用データセット.xlsx
+++ b/excel/20260805_タイムレコード_03_検証用データセット.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>OP-211・CA-001〜004。D2-1 の行を複製して増やす</t>
+          <t>OP-211・CA-001〜004。D2-1 の行を複製して増やす。ほかに使う検証: CA-003 / OP-219</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>OP-021・OP-022・OP-031。手入力のセルフスタート検証の起点</t>
+          <t>OP-021・OP-022・OP-031。手入力のセルフスタート検証の起点。ほかに使う検証: OP-001 / OP-620</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>①業態の正常系</t>
+          <t>①業態の正常系。D1（①業態）としてまとめて使う検証: OP-021 / OP-031 / OP-108 / OP-201 / OP-312 / OP-501 / OP-601 / OP-612 / OP-617 / OP-620 / OP-707</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>①業態の正常系</t>
+          <t>①業態の正常系。D1（①業態）としてまとめて使う検証: OP-021 / OP-031 / OP-108 / OP-201 / OP-312 / OP-501 / OP-601 / OP-612 / OP-617 / OP-620 / OP-707</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>正常系。D2（②店舗）としてまとめて使う検証: OP-202 / OP-219 / OP-312 / OP-601 / OP-707</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>郵便番号が空欄（OP-303）</t>
+          <t>郵便番号が空欄（OP-303）。ほかに使う検証: OP-404</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>未登録の業態名（OP-304）</t>
+          <t>未登録の業態名（OP-304）。ほかに使う検証: OP-404</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>コードは空欄で自動採番</t>
+          <t>コードは空欄で自動採番。D3（③雇用区分）としてまとめて使う検証: OP-601 / OP-705 / OP-707</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>③雇用区分の正常系（時給・月次契約労働時間は空欄）</t>
+          <t>③雇用区分の正常系（時給・月次契約労働時間は空欄）。D3（③雇用区分）としてまとめて使う検証: OP-601 / OP-705 / OP-707</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>給与体系は時給・月給のみ</t>
+          <t>給与体系は時給・月給のみ。ほかに使う検証: OP-218</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>④従業員の正常系。OP-604・OP-701</t>
+          <t>④従業員の正常系。OP-604・OP-701。ほかに使う検証: OP-311</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>④従業員の正常系</t>
+          <t>④従業員の正常系。D4（④従業員）としてまとめて使う検証: OP-031 / OP-215 / OP-505 / OP-604 / OP-605 / OP-612 / OP-701 / OP-702 / OP-703</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>④従業員の正常系（日額の交通費）</t>
+          <t>④従業員の正常系（日額の交通費）。D4（④従業員）としてまとめて使う検証: OP-031 / OP-215 / OP-505 / OP-604 / OP-605 / OP-612 / OP-701 / OP-702 / OP-703</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>④従業員の正常系（新宿店）</t>
+          <t>④従業員の正常系（新宿店）。D4（④従業員）としてまとめて使う検証: OP-031 / OP-215 / OP-505 / OP-604 / OP-605 / OP-612 / OP-701 / OP-702 / OP-703</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>OP-607で渋谷店を画面から追加し2店舗にする</t>
+          <t>OP-607で渋谷店を画面から追加し2店舗にする。ほかに使う検証: OP-608</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>会社内に未登録のメールアドレス。OP-308 の「新規登録」判定に使う</t>
+          <t>会社内に未登録のメールアドレス。OP-308 の「新規登録」判定に使う。ほかに使う検証: OP-704</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>④で登録し招待承諾済みの従業員。CA-061の対象</t>
+          <t>④で登録し招待承諾済みの従業員。CA-061の対象。ほかに使う検証: OP-607</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>④で登録し招待未承諾の従業員</t>
+          <t>④で登録し招待未承諾の従業員。D5（⑤管理者）としてまとめて使う検証: OP-308 / OP-505 / OP-606 / OP-620</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>D5-1 を取り込んだ後に再度取り込む。OP-308 の「スキップ」判定に使う（同じ値でよい）</t>
+          <t>D5-1 を取り込んだ後に再度取り込む。OP-308 の「スキップ」判定に使う（同じ値でよい）。ほかに使う検証: OP-704</t>
         </is>
       </c>
     </row>
